--- a/ImportExportExcellApi/Templates/Employee_Template.xlsx
+++ b/ImportExportExcellApi/Templates/Employee_Template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="23040" windowHeight="8280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -160,10 +160,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -632,16 +632,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -774,7 +774,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -789,12 +789,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -804,7 +798,7 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
@@ -1069,6 +1063,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1330,14 +1331,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:T5"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15.75" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9.13888888888889" defaultRowHeight="15.6" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="2" width="20.7142857142857" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7142857142857" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.7142857142857" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.7142857142857" style="2" customWidth="1"/>
-    <col min="6" max="18" width="20.7142857142857" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.14285714285714" style="1"/>
+    <col min="1" max="2" width="20.712962962963" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.712962962963" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.712962962963" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.712962962963" style="2" customWidth="1"/>
+    <col min="6" max="18" width="20.712962962963" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.13888888888889" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -1402,14 +1403,14 @@
       <c r="E3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="5"/>
+      <c r="F3" s="4"/>
       <c r="G3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J3" s="3" t="s">
